--- a/Framework_MWC_Testing/BaoCao/Test chức năng.xlsx
+++ b/Framework_MWC_Testing/BaoCao/Test chức năng.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="8380" tabRatio="877" activeTab="5"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="8380" tabRatio="877" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Chung" sheetId="22" r:id="rId1"/>
@@ -17,7 +17,8 @@
     <sheet name="Đăng ký" sheetId="2" r:id="rId3"/>
     <sheet name="Tìm kiếm sản phẩm" sheetId="4" r:id="rId4"/>
     <sheet name="Thông tin cá nhân" sheetId="19" r:id="rId5"/>
-    <sheet name="Đánh giá sản phẩm" sheetId="24" r:id="rId6"/>
+    <sheet name="Đặt hàng" sheetId="26" r:id="rId6"/>
+    <sheet name="Đánh giá sản phẩm" sheetId="24" r:id="rId7"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="314">
   <si>
     <t>STT</t>
   </si>
@@ -1433,6 +1434,255 @@
   </si>
   <si>
     <t>Đánh giá sản phẩm không thành công - Email chứa ký tự đặc biệt "@"</t>
+  </si>
+  <si>
+    <t>Đặt hàng</t>
+  </si>
+  <si>
+    <t>DH-1</t>
+  </si>
+  <si>
+    <t>DH-2</t>
+  </si>
+  <si>
+    <t>DH-3</t>
+  </si>
+  <si>
+    <t>DH-4</t>
+  </si>
+  <si>
+    <t>DH-5</t>
+  </si>
+  <si>
+    <t>DH-6</t>
+  </si>
+  <si>
+    <t>DH-7</t>
+  </si>
+  <si>
+    <t>DH-8</t>
+  </si>
+  <si>
+    <t>DH-9</t>
+  </si>
+  <si>
+    <t>Đặt hàng thành công</t>
+  </si>
+  <si>
+    <t>Kiểm tra người dùng có thể đặt hàng thành công</t>
+  </si>
+  <si>
+    <t>Sản phẩm còn hàng</t>
+  </si>
+  <si>
+    <t>1. Nhập Tên sản phẩm muốn mua vào ô tìm kiếm
+VD: Giày Cao Gót MWC 4431
+2. Chọn màu sắc, size
+VD: bạc, 39
+3. Nhấn Mua ngay
+4. Nhập tên
+VD: Phạm Ánh Dương
+5. Nhập SĐT
+VD: 0905123456
+6. Nhập Address
+VD: 123 Lý Thường Kiệt
+7. Chọn Tỉnh
+VD: TP Hồ Chí Minh
+8. Chọn Quận/Huyện
+VD: Quận 1
+9. Chọn Xã/Phưỡng
+VD: Phường Bến Nghé
+10. Nhấn "Đặt hàng"</t>
+  </si>
+  <si>
+    <t>1. Nhập Tên sản phẩm muốn mua vào ô tìm kiếm
+VD: Giày Cao Gót MWC 4431
+2. Chọn màu sắc, size
+VD: bạc, 36
+3. Nhấn Mua ngay
+4. Bỏ tên
+5. Nhập SĐT
+VD: 0905123456
+6. Nhập Address
+VD: 123 ABC
+7. Chọn Tỉnh
+VD: TP Cần Thơ
+8. Chọn Quận/Huyện
+VD: Quận Ninh Kiều
+9. Chọn Xã/Phưỡng
+VD: Phường An Bình
+10. Nhấn "Đặt hàng"</t>
+  </si>
+  <si>
+    <t>Hiển thị thông báo "Bạn chưa nhập thông tin nhận hàng!"
+Đặt hàng không thành công</t>
+  </si>
+  <si>
+    <t>Hiển thị thông báo "Đặt hàng thành công!"
+Đặt hàng thành công</t>
+  </si>
+  <si>
+    <t>Bỏ trống thông tin - Họ tên</t>
+  </si>
+  <si>
+    <t>Bỏ trống thông tin - SĐT</t>
+  </si>
+  <si>
+    <t>1. Nhập Tên sản phẩm muốn mua vào ô tìm kiếm
+VD: Giày Cao Gót MWC 4431
+2. Chọn màu sắc, size
+VD: đen, 35
+3. Nhấn Mua ngay
+4. Nhập tên
+VD: Ánh Dương
+5. Bỏ SĐT
+6. Nhập Address
+VD: 123 ABC
+7. Chọn Tỉnh
+VD: TP Hồ Chí Minh
+8. Chọn Quận/Huyện
+VD: Quận 1
+9. Chọn Xã/Phưỡng
+VD: Phường Bến Nghé
+10. Nhấn "Đặt hàng"</t>
+  </si>
+  <si>
+    <t>Bỏ trống thông tin - Địa chỉ</t>
+  </si>
+  <si>
+    <t>1. Nhập Tên sản phẩm muốn mua vào ô tìm kiếm
+VD: Giày Cao Gót MWC 4431
+2. Chọn màu sắc, size
+VD: đen, 38
+3. Nhấn Mua ngay
+4. Nhập tên
+VD: Phạm Ánh
+5. Nhập SĐT
+VD: 0905123456
+6. Bỏ Address
+7. Chọn Tỉnh
+VD: Tây Ninh
+8. Chọn Quận/Huyện
+VD: Huyện Tân Châu
+9. Chọn Xã/Phưỡng
+VD: Xã Suối Ngô
+10. Nhấn "Đặt hàng"</t>
+  </si>
+  <si>
+    <t>Bỏ trống thông tin - Không chọn Tỉnh - Quận/Huyện - Xã/Phường</t>
+  </si>
+  <si>
+    <t>1. Nhập Tên sản phẩm muốn mua vào ô tìm kiếm
+VD: Giày Cao Gót MWC 4431
+2. Chọn màu sắc, size
+VD: đen, 38
+3. Nhấn Mua ngay
+4. Nhập tên
+VD: Phạm Dương
+5. Nhập SĐT
+VD: 0905123456
+6. Nhập Address
+VD: 123 Lý Thường Kiệt
+7. Bỏ chọn Tỉnh
+8. Bỏ chọn Quận/Huyện
+9. Bỏ chọn Xã/Phưỡng
+10. Nhấn "Đặt hàng"</t>
+  </si>
+  <si>
+    <t>Số điện thoại không đúng định dạng &lt; 10 ký tự số</t>
+  </si>
+  <si>
+    <t>1. Nhập Tên sản phẩm muốn mua vào ô tìm kiếm
+VD: Giày Cao Gót MWC 4431
+2. Chọn màu sắc, size
+VD: bạc, 37
+3. Nhấn Mua ngay
+4. Nhập tên
+VD:Ánh Dương
+5. Nhập SĐT
+VD: 3321156
+6. Nhập Address
+VD: 456 DEF
+7. Chọn Tỉnh
+VD: TP Hồ Chí Minh
+8. Chọn Quận/Huyện
+VD: Quận 10
+9. Chọn Xã/Phưỡng
+VD: Phường 1
+10. Nhấn "Đặt hàng"</t>
+  </si>
+  <si>
+    <t>Hiển thị thông báo "SĐT không đúng định dạng"
+Đặt hàng không thành công</t>
+  </si>
+  <si>
+    <t>Số điện thoại không đúng định dạng &gt; 10 ký tự số</t>
+  </si>
+  <si>
+    <t>1. Nhập Tên sản phẩm muốn mua vào ô tìm kiếm
+VD: Giày Cao Gót MWC 4431
+2. Chọn màu sắc, size
+VD: bạc, 35
+3. Nhấn Mua ngay
+4. Nhập tên
+VD: Phạm Ánh Dương
+5. Nhập SĐT
+VD: 0905123456666
+6. Nhập Address
+VD: 123 Lý Thường Kiệt
+7. Chọn Tỉnh
+VD: Hậu Giang
+8. Chọn Quận/Huyện
+VD: Huyện Châu Thành A
+9. Chọn Xã/Phưỡng
+VD: Thị trấn Bảy Ngàn
+10. Nhấn "Đặt hàng"</t>
+  </si>
+  <si>
+    <t>Số điện thoại không đúng định dạng chứa ký tự đặc biệt</t>
+  </si>
+  <si>
+    <t>1. Nhập Tên sản phẩm muốn mua vào ô tìm kiếm
+VD: Giày Cao Gót MWC 4431
+2. Chọn màu sắc, size
+VD: bạc, 36
+3. Nhấn Mua ngay
+4. Nhập tên
+VD: Phạm Dương
+5. Nhập SĐT
+VD: 090512345@
+6. Nhập Address
+VD: 123 ABC
+7. Chọn Tỉnh
+VD: Tiền Giang
+8. Chọn Quận/Huyện
+VD: Thành phố Mỹ Tho
+9. Chọn Xã/Phưỡng
+VD: Phường 10
+10. Nhấn "Đặt hàng"</t>
+  </si>
+  <si>
+    <t>Số điện thoại không đúng định dạng chứa ký tự chữ</t>
+  </si>
+  <si>
+    <t>1. Nhập Tên sản phẩm muốn mua vào ô tìm kiếm
+VD: Giày Cao Gót MWC 4431
+2. Chọn màu sắc, size
+VD: đen, 35
+3. Nhấn Mua ngay
+4. Nhập tên
+VD: Ánh Dương
+5. Nhập SĐT
+VD: 09051234ba
+6. Nhập Address
+VD: 456 DEF
+7. Chọn Tỉnh
+VD: Vĩnh Long
+8. Chọn Quận/Huyện
+VD: Huyện Trà Ôn
+9. Chọn Xã/Phưỡng
+VD: Thị trấn Trà Ôn
+10. Nhấn "Đặt hàng"</t>
   </si>
 </sst>
 </file>
@@ -2075,6 +2325,18 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="27" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2083,18 +2345,6 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="27" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2103,7 +2353,35 @@
     <cellStyle name="Normal_Sheet1" xfId="2"/>
     <cellStyle name="Percent" xfId="3" builtinId="5"/>
   </cellStyles>
-  <dxfs count="39">
+  <dxfs count="43">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF7C80"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -2454,25 +2732,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
-      <tableStyleElement type="wholeTable" dxfId="38"/>
-      <tableStyleElement type="headerRow" dxfId="37"/>
-      <tableStyleElement type="totalRow" dxfId="36"/>
-      <tableStyleElement type="firstColumn" dxfId="35"/>
-      <tableStyleElement type="lastColumn" dxfId="34"/>
+      <tableStyleElement type="wholeTable" dxfId="42"/>
+      <tableStyleElement type="headerRow" dxfId="41"/>
+      <tableStyleElement type="totalRow" dxfId="40"/>
+      <tableStyleElement type="firstColumn" dxfId="39"/>
+      <tableStyleElement type="lastColumn" dxfId="38"/>
+      <tableStyleElement type="firstRowStripe" dxfId="37"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="36"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
+      <tableStyleElement type="headerRow" dxfId="35"/>
+      <tableStyleElement type="totalRow" dxfId="34"/>
       <tableStyleElement type="firstRowStripe" dxfId="33"/>
       <tableStyleElement type="firstColumnStripe" dxfId="32"/>
-    </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
-      <tableStyleElement type="headerRow" dxfId="31"/>
-      <tableStyleElement type="totalRow" dxfId="30"/>
-      <tableStyleElement type="firstRowStripe" dxfId="29"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="28"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="27"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="26"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="25"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="24"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="23"/>
-      <tableStyleElement type="pageFieldValues" dxfId="22"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="31"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="30"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="29"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="28"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="27"/>
+      <tableStyleElement type="pageFieldValues" dxfId="26"/>
     </tableStyle>
   </tableStyles>
   <colors>
@@ -2750,7 +3028,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="10.26953125" style="58" customWidth="1"/>
@@ -2858,7 +3136,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="26">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" s="27" t="s">
         <v>7</v>
@@ -2881,105 +3159,128 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="26">
+        <v>5</v>
+      </c>
+      <c r="B6" s="27" t="s">
+        <v>281</v>
+      </c>
+      <c r="C6" s="26">
+        <v>9</v>
+      </c>
+      <c r="D6" s="26">
         <v>4</v>
       </c>
-      <c r="B6" s="27" t="s">
-        <v>221</v>
-      </c>
-      <c r="C6" s="26">
-        <v>13</v>
-      </c>
-      <c r="D6" s="26">
-        <v>6</v>
-      </c>
       <c r="E6" s="26">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F6" s="60">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G6" s="60">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" s="59" customFormat="1" ht="27.5" customHeight="1">
-      <c r="A8" s="96" t="s">
+    <row r="7" spans="1:7">
+      <c r="A7" s="26">
+        <v>5</v>
+      </c>
+      <c r="B7" s="27" t="s">
+        <v>221</v>
+      </c>
+      <c r="C7" s="26">
+        <v>13</v>
+      </c>
+      <c r="D7" s="26">
+        <v>6</v>
+      </c>
+      <c r="E7" s="26">
+        <v>7</v>
+      </c>
+      <c r="F7" s="60">
+        <v>13</v>
+      </c>
+      <c r="G7" s="60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" s="59" customFormat="1" ht="27.5" customHeight="1">
+      <c r="A9" s="100" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="97"/>
-      <c r="C8" s="28">
+      <c r="B9" s="101"/>
+      <c r="C9" s="28">
         <f>SUM(C2:C6)</f>
-        <v>60</v>
-      </c>
-      <c r="D8" s="63">
+        <v>56</v>
+      </c>
+      <c r="D9" s="63">
         <f>SUM(D2:D6)</f>
-        <v>45</v>
-      </c>
-      <c r="E8" s="65">
+        <v>43</v>
+      </c>
+      <c r="E9" s="65">
         <f>SUM(E2:E6)</f>
-        <v>16</v>
-      </c>
-      <c r="F8" s="67">
+        <v>14</v>
+      </c>
+      <c r="F9" s="67">
         <f>SUM(F2:F6)</f>
-        <v>60</v>
-      </c>
-      <c r="G8" s="69">
+        <v>56</v>
+      </c>
+      <c r="G9" s="69">
         <f>SUM(G2:G6)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="14.5" customHeight="1">
-      <c r="A9" s="95" t="s">
+    <row r="10" spans="1:7" ht="14.5" customHeight="1">
+      <c r="A10" s="99" t="s">
         <v>61</v>
       </c>
-      <c r="B9" s="95"/>
-      <c r="C9" s="71">
-        <f>C8/$C$8</f>
+      <c r="B10" s="99"/>
+      <c r="C10" s="71">
+        <f>C9/$C$9</f>
         <v>1</v>
       </c>
-      <c r="D9" s="64">
-        <f>D8/$C$8</f>
-        <v>0.75</v>
-      </c>
-      <c r="E9" s="66">
-        <f>E8/$C$8</f>
-        <v>0.26666666666666666</v>
-      </c>
-      <c r="F9" s="68">
-        <f>F8/$C$8</f>
+      <c r="D10" s="64">
+        <f>D9/$C$9</f>
+        <v>0.7678571428571429</v>
+      </c>
+      <c r="E10" s="66">
+        <f>E9/$C$9</f>
+        <v>0.25</v>
+      </c>
+      <c r="F10" s="68">
+        <f>F9/$C$9</f>
         <v>1</v>
       </c>
-      <c r="G9" s="70">
-        <f>G8/$C$8</f>
+      <c r="G10" s="70">
+        <f>G9/$C$9</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="B10" s="59"/>
     </row>
     <row r="11" spans="1:7">
       <c r="B11" s="59"/>
     </row>
-    <row r="18" spans="11:12">
-      <c r="K18" s="59" t="s">
-        <v>52</v>
-      </c>
-      <c r="L18" s="58" t="s">
-        <v>55</v>
-      </c>
+    <row r="12" spans="1:7">
+      <c r="B12" s="59"/>
     </row>
     <row r="19" spans="11:12">
       <c r="K19" s="59" t="s">
+        <v>52</v>
+      </c>
+      <c r="L19" s="58" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="20" spans="11:12">
+      <c r="K20" s="59" t="s">
         <v>51</v>
       </c>
-      <c r="L19" s="58" t="s">
+      <c r="L20" s="58" t="s">
         <v>56</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A10:B10"/>
     <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A8:B8"/>
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2989,8 +3290,8 @@
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="containsText" priority="4" operator="containsText" id="{4D3815A5-E425-416B-BF06-D1C62615CAD5}">
-            <xm:f>NOT(ISERROR(SEARCH($B$10,B10)))</xm:f>
-            <xm:f>$B$10</xm:f>
+            <xm:f>NOT(ISERROR(SEARCH($B$11,B11)))</xm:f>
+            <xm:f>$B$11</xm:f>
             <x14:dxf>
               <font>
                 <color auto="1"/>
@@ -3002,12 +3303,12 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>B10:B11</xm:sqref>
+          <xm:sqref>B11:B12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="containsText" priority="3" operator="containsText" id="{E31D92C5-71C6-45B1-845A-3E71CDBFAE44}">
-            <xm:f>NOT(ISERROR(SEARCH($B$11,B11)))</xm:f>
-            <xm:f>$B$11</xm:f>
+            <xm:f>NOT(ISERROR(SEARCH($B$12,B12)))</xm:f>
+            <xm:f>$B$12</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -3016,7 +3317,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>B11</xm:sqref>
+          <xm:sqref>B12</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -3650,8 +3951,8 @@
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="containsText" priority="6" operator="containsText" id="{EA0FB0CC-DEE3-4298-A7DB-71C631DE29FC}">
-            <xm:f>NOT(ISERROR(SEARCH(Chung!$K$19,H5)))</xm:f>
-            <xm:f>Chung!$K$19</xm:f>
+            <xm:f>NOT(ISERROR(SEARCH(Chung!$K$20,H5)))</xm:f>
+            <xm:f>Chung!$K$20</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -3661,8 +3962,8 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="containsText" priority="7" operator="containsText" id="{2F8D11B2-60B9-4149-AA64-429B14713A96}">
-            <xm:f>NOT(ISERROR(SEARCH(Chung!$K$18,H5)))</xm:f>
-            <xm:f>Chung!$K$18</xm:f>
+            <xm:f>NOT(ISERROR(SEARCH(Chung!$K$19,H5)))</xm:f>
+            <xm:f>Chung!$K$19</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -3675,8 +3976,8 @@
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="containsText" priority="8" operator="containsText" id="{17EE5443-D867-4E0A-B44E-A6955851D2A4}">
-            <xm:f>NOT(ISERROR(SEARCH(Chung!$L$19,I5)))</xm:f>
-            <xm:f>Chung!$L$19</xm:f>
+            <xm:f>NOT(ISERROR(SEARCH(Chung!$L$20,I5)))</xm:f>
+            <xm:f>Chung!$L$20</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -3686,8 +3987,8 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="containsText" priority="9" operator="containsText" id="{178B32A1-4D0F-4593-B37C-3EA88C1C1547}">
-            <xm:f>NOT(ISERROR(SEARCH(Chung!$L$18,I5)))</xm:f>
-            <xm:f>Chung!$L$18</xm:f>
+            <xm:f>NOT(ISERROR(SEARCH(Chung!$L$19,I5)))</xm:f>
+            <xm:f>Chung!$L$19</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -3704,13 +4005,13 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>Chung!$K$18:$K$19</xm:f>
+            <xm:f>Chung!$K$19:$K$20</xm:f>
           </x14:formula1>
           <xm:sqref>H5:H19</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>Chung!$L$18:$L$19</xm:f>
+            <xm:f>Chung!$L$19:$L$20</xm:f>
           </x14:formula1>
           <xm:sqref>I5:I19</xm:sqref>
         </x14:dataValidation>
@@ -4244,8 +4545,8 @@
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="containsText" priority="10" operator="containsText" id="{4DF980DA-F797-409B-9BA0-898BADEB1F9B}">
-            <xm:f>NOT(ISERROR(SEARCH(Chung!$K$19,H5)))</xm:f>
-            <xm:f>Chung!$K$19</xm:f>
+            <xm:f>NOT(ISERROR(SEARCH(Chung!$K$20,H5)))</xm:f>
+            <xm:f>Chung!$K$20</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -4255,8 +4556,8 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="containsText" priority="11" operator="containsText" id="{CA0AA74A-E7D7-4FE8-99AF-36A2A601D2DD}">
-            <xm:f>NOT(ISERROR(SEARCH(Chung!$K$18,H5)))</xm:f>
-            <xm:f>Chung!$K$18</xm:f>
+            <xm:f>NOT(ISERROR(SEARCH(Chung!$K$19,H5)))</xm:f>
+            <xm:f>Chung!$K$19</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -4269,8 +4570,8 @@
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="containsText" priority="12" operator="containsText" id="{2B7C12E2-1B7D-4823-BB39-7C741B8F1A5A}">
-            <xm:f>NOT(ISERROR(SEARCH(Chung!$L$19,I5)))</xm:f>
-            <xm:f>Chung!$L$19</xm:f>
+            <xm:f>NOT(ISERROR(SEARCH(Chung!$L$20,I5)))</xm:f>
+            <xm:f>Chung!$L$20</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -4280,8 +4581,8 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="containsText" priority="13" operator="containsText" id="{E137D0FC-1DD2-41BE-AC71-3B415426980E}">
-            <xm:f>NOT(ISERROR(SEARCH(Chung!$L$18,I5)))</xm:f>
-            <xm:f>Chung!$L$18</xm:f>
+            <xm:f>NOT(ISERROR(SEARCH(Chung!$L$19,I5)))</xm:f>
+            <xm:f>Chung!$L$19</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -4298,13 +4599,13 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>Chung!$K$18:$K$19</xm:f>
+            <xm:f>Chung!$K$19:$K$20</xm:f>
           </x14:formula1>
           <xm:sqref>H5:H18</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>Chung!$L$18:$L$19</xm:f>
+            <xm:f>Chung!$L$19:$L$20</xm:f>
           </x14:formula1>
           <xm:sqref>I5:I18</xm:sqref>
         </x14:dataValidation>
@@ -5048,8 +5349,8 @@
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="containsText" priority="14" operator="containsText" id="{167B4CBA-F46C-4E08-9CD6-AF317DC66F51}">
-            <xm:f>NOT(ISERROR(SEARCH(Chung!$K$19,H5)))</xm:f>
-            <xm:f>Chung!$K$19</xm:f>
+            <xm:f>NOT(ISERROR(SEARCH(Chung!$K$20,H5)))</xm:f>
+            <xm:f>Chung!$K$20</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -5059,8 +5360,8 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="containsText" priority="15" operator="containsText" id="{D6C9701B-3C25-411B-9C2F-FCA876FE595C}">
-            <xm:f>NOT(ISERROR(SEARCH(Chung!$K$18,H5)))</xm:f>
-            <xm:f>Chung!$K$18</xm:f>
+            <xm:f>NOT(ISERROR(SEARCH(Chung!$K$19,H5)))</xm:f>
+            <xm:f>Chung!$K$19</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -5073,8 +5374,8 @@
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="containsText" priority="16" operator="containsText" id="{C1B0DEAD-A781-4C62-A7CF-FF929C11B14A}">
-            <xm:f>NOT(ISERROR(SEARCH(Chung!$L$19,I5)))</xm:f>
-            <xm:f>Chung!$L$19</xm:f>
+            <xm:f>NOT(ISERROR(SEARCH(Chung!$L$20,I5)))</xm:f>
+            <xm:f>Chung!$L$20</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -5084,8 +5385,8 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="containsText" priority="17" operator="containsText" id="{2C913F78-7E8A-4F17-A0A3-6971424A9470}">
-            <xm:f>NOT(ISERROR(SEARCH(Chung!$L$18,I5)))</xm:f>
-            <xm:f>Chung!$L$18</xm:f>
+            <xm:f>NOT(ISERROR(SEARCH(Chung!$L$19,I5)))</xm:f>
+            <xm:f>Chung!$L$19</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -5102,13 +5403,13 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>Chung!$K$18:$K$19</xm:f>
+            <xm:f>Chung!$K$19:$K$20</xm:f>
           </x14:formula1>
           <xm:sqref>H5:H15</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>Chung!$L$18:$L$19</xm:f>
+            <xm:f>Chung!$L$19:$L$20</xm:f>
           </x14:formula1>
           <xm:sqref>I5:I15</xm:sqref>
         </x14:dataValidation>
@@ -5130,7 +5431,7 @@
     <col min="2" max="2" width="24.26953125" style="13" customWidth="1"/>
     <col min="3" max="3" width="23.90625" style="13" customWidth="1"/>
     <col min="4" max="4" width="35.81640625" style="13" customWidth="1"/>
-    <col min="5" max="5" width="34.54296875" style="101" customWidth="1"/>
+    <col min="5" max="5" width="34.54296875" style="98" customWidth="1"/>
     <col min="6" max="6" width="25" style="13" customWidth="1"/>
     <col min="7" max="7" width="24.08984375" style="13" customWidth="1"/>
     <col min="8" max="8" width="8.90625" style="13"/>
@@ -5150,7 +5451,7 @@
         <f>"Pass: "&amp;COUNTIF(#REF!,"Pass")</f>
         <v>#REF!</v>
       </c>
-      <c r="E1" s="98" t="e">
+      <c r="E1" s="95" t="e">
         <f>"Untested: "&amp;COUNTIF(#REF!,"Untest")</f>
         <v>#REF!</v>
       </c>
@@ -5169,7 +5470,7 @@
         <f>"Fail: "&amp;COUNTIF(#REF!,"Fail")</f>
         <v>#REF!</v>
       </c>
-      <c r="E2" s="98" t="e">
+      <c r="E2" s="95" t="e">
         <f>"N/A: "&amp;COUNTIF(#REF!,"N/A")</f>
         <v>#REF!</v>
       </c>
@@ -5188,7 +5489,7 @@
         <f>"Percent Complete: "&amp;ROUND((COUNTIF(#REF!,"Pass")*100)/((COUNTA($A$5:$A$872)*5)-COUNTIF(#REF!,"N/A")),2)&amp;"%"</f>
         <v>#REF!</v>
       </c>
-      <c r="E3" s="99" t="str">
+      <c r="E3" s="96" t="str">
         <f>"Number of cases: "&amp;(COUNTA($A$5:$A$872))</f>
         <v>Number of cases: 14</v>
       </c>
@@ -5208,7 +5509,7 @@
       <c r="D4" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="100" t="s">
+      <c r="E4" s="97" t="s">
         <v>18</v>
       </c>
       <c r="F4" s="11" t="s">
@@ -5763,8 +6064,8 @@
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="containsText" priority="26" operator="containsText" id="{CB9A6FB6-FAB9-411A-A293-3EC5B790E827}">
-            <xm:f>NOT(ISERROR(SEARCH(Chung!$K$19,H5)))</xm:f>
-            <xm:f>Chung!$K$19</xm:f>
+            <xm:f>NOT(ISERROR(SEARCH(Chung!$K$20,H5)))</xm:f>
+            <xm:f>Chung!$K$20</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -5774,8 +6075,8 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="containsText" priority="27" operator="containsText" id="{38317E70-E360-4E81-9612-401AA3840913}">
-            <xm:f>NOT(ISERROR(SEARCH(Chung!$K$18,H5)))</xm:f>
-            <xm:f>Chung!$K$18</xm:f>
+            <xm:f>NOT(ISERROR(SEARCH(Chung!$K$19,H5)))</xm:f>
+            <xm:f>Chung!$K$19</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -5788,8 +6089,8 @@
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="containsText" priority="28" operator="containsText" id="{7E6DFF63-4CC4-4CA4-83AF-CE3DC9588243}">
-            <xm:f>NOT(ISERROR(SEARCH(Chung!$L$19,I5)))</xm:f>
-            <xm:f>Chung!$L$19</xm:f>
+            <xm:f>NOT(ISERROR(SEARCH(Chung!$L$20,I5)))</xm:f>
+            <xm:f>Chung!$L$20</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -5799,8 +6100,8 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="containsText" priority="29" operator="containsText" id="{EB2E0EB0-B10D-4E61-B09D-9B5BD4ADC7B3}">
-            <xm:f>NOT(ISERROR(SEARCH(Chung!$L$18,I5)))</xm:f>
-            <xm:f>Chung!$L$18</xm:f>
+            <xm:f>NOT(ISERROR(SEARCH(Chung!$L$19,I5)))</xm:f>
+            <xm:f>Chung!$L$19</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -5817,13 +6118,13 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>Chung!$K$18:$K$19</xm:f>
+            <xm:f>Chung!$K$19:$K$20</xm:f>
           </x14:formula1>
           <xm:sqref>H5:H18</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>Chung!$L$18:$L$19</xm:f>
+            <xm:f>Chung!$L$19:$L$20</xm:f>
           </x14:formula1>
           <xm:sqref>I5:I18</xm:sqref>
         </x14:dataValidation>
@@ -5838,6 +6139,719 @@
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
+  <dimension ref="A1:K38"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="1" width="17.36328125" style="42" customWidth="1"/>
+    <col min="2" max="2" width="23.54296875" style="44" customWidth="1"/>
+    <col min="3" max="3" width="38.90625" style="44" customWidth="1"/>
+    <col min="4" max="4" width="24.54296875" style="44" customWidth="1"/>
+    <col min="5" max="5" width="41.1796875" style="44" customWidth="1"/>
+    <col min="6" max="6" width="30.90625" style="44" customWidth="1"/>
+    <col min="7" max="7" width="31.6328125" style="44" customWidth="1"/>
+    <col min="8" max="8" width="11.453125" style="45" customWidth="1"/>
+    <col min="9" max="9" width="9.6328125" style="42" customWidth="1"/>
+    <col min="10" max="16384" width="8.90625" style="44"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" s="34" customFormat="1" ht="46" customHeight="1">
+      <c r="A1" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="30"/>
+      <c r="D1" s="31" t="e">
+        <f>"Pass: "&amp;COUNTIF(#REF!,"Pass")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E1" s="32" t="e">
+        <f>"Untested: "&amp;COUNTIF(#REF!,"Untest")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F1" s="33"/>
+      <c r="I1" s="56"/>
+    </row>
+    <row r="2" spans="1:11" s="34" customFormat="1" ht="28" customHeight="1">
+      <c r="A2" s="35" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="36" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="36"/>
+      <c r="D2" s="31" t="e">
+        <f>"Fail: "&amp;COUNTIF(#REF!,"Fail")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E2" s="32" t="e">
+        <f>"N/A: "&amp;COUNTIF(#REF!,"N/A")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F2" s="33"/>
+      <c r="I2" s="56"/>
+    </row>
+    <row r="3" spans="1:11" s="34" customFormat="1" ht="28" customHeight="1">
+      <c r="A3" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="35" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" s="35"/>
+      <c r="D3" s="31" t="e">
+        <f>"Percent Complete: "&amp;ROUND((COUNTIF(#REF!,"Pass")*100)/((COUNTA($A$5:$A$957)*5)-COUNTIF(#REF!,"N/A")),2)&amp;"%"</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E3" s="37" t="str">
+        <f>"Number of cases: "&amp;(COUNTA($A$5:$A$957))</f>
+        <v>Number of cases: 9</v>
+      </c>
+      <c r="F3" s="38"/>
+      <c r="I3" s="56"/>
+    </row>
+    <row r="4" spans="1:11" s="42" customFormat="1" ht="42" customHeight="1">
+      <c r="A4" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="39" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="39" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" s="41" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" s="52" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="330.5" customHeight="1">
+      <c r="A5" s="48" t="s">
+        <v>282</v>
+      </c>
+      <c r="B5" s="48" t="s">
+        <v>291</v>
+      </c>
+      <c r="C5" s="50" t="s">
+        <v>292</v>
+      </c>
+      <c r="D5" s="50" t="s">
+        <v>293</v>
+      </c>
+      <c r="E5" s="43" t="s">
+        <v>294</v>
+      </c>
+      <c r="F5" s="43" t="s">
+        <v>297</v>
+      </c>
+      <c r="G5" s="43" t="s">
+        <v>297</v>
+      </c>
+      <c r="H5" s="48" t="s">
+        <v>52</v>
+      </c>
+      <c r="I5" s="48" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="330.5" customHeight="1">
+      <c r="A6" s="48" t="s">
+        <v>283</v>
+      </c>
+      <c r="B6" s="48" t="s">
+        <v>298</v>
+      </c>
+      <c r="C6" s="50" t="s">
+        <v>292</v>
+      </c>
+      <c r="D6" s="50" t="s">
+        <v>293</v>
+      </c>
+      <c r="E6" s="43" t="s">
+        <v>295</v>
+      </c>
+      <c r="F6" s="43" t="s">
+        <v>296</v>
+      </c>
+      <c r="G6" s="43" t="s">
+        <v>296</v>
+      </c>
+      <c r="H6" s="48" t="s">
+        <v>52</v>
+      </c>
+      <c r="I6" s="48" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="330.5" customHeight="1">
+      <c r="A7" s="48" t="s">
+        <v>284</v>
+      </c>
+      <c r="B7" s="48" t="s">
+        <v>299</v>
+      </c>
+      <c r="C7" s="50" t="s">
+        <v>292</v>
+      </c>
+      <c r="D7" s="50" t="s">
+        <v>293</v>
+      </c>
+      <c r="E7" s="43" t="s">
+        <v>300</v>
+      </c>
+      <c r="F7" s="43" t="s">
+        <v>296</v>
+      </c>
+      <c r="G7" s="43" t="s">
+        <v>296</v>
+      </c>
+      <c r="H7" s="48" t="s">
+        <v>52</v>
+      </c>
+      <c r="I7" s="48" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="330.5" customHeight="1">
+      <c r="A8" s="48" t="s">
+        <v>285</v>
+      </c>
+      <c r="B8" s="48" t="s">
+        <v>301</v>
+      </c>
+      <c r="C8" s="50" t="s">
+        <v>292</v>
+      </c>
+      <c r="D8" s="50" t="s">
+        <v>293</v>
+      </c>
+      <c r="E8" s="43" t="s">
+        <v>302</v>
+      </c>
+      <c r="F8" s="43" t="s">
+        <v>296</v>
+      </c>
+      <c r="G8" s="43" t="s">
+        <v>297</v>
+      </c>
+      <c r="H8" s="48" t="s">
+        <v>51</v>
+      </c>
+      <c r="I8" s="48" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" s="46" customFormat="1" ht="330.5" customHeight="1">
+      <c r="A9" s="48" t="s">
+        <v>286</v>
+      </c>
+      <c r="B9" s="48" t="s">
+        <v>303</v>
+      </c>
+      <c r="C9" s="50" t="s">
+        <v>292</v>
+      </c>
+      <c r="D9" s="50" t="s">
+        <v>293</v>
+      </c>
+      <c r="E9" s="43" t="s">
+        <v>304</v>
+      </c>
+      <c r="F9" s="43" t="s">
+        <v>296</v>
+      </c>
+      <c r="G9" s="43" t="s">
+        <v>296</v>
+      </c>
+      <c r="H9" s="48" t="s">
+        <v>52</v>
+      </c>
+      <c r="I9" s="48" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" s="46" customFormat="1" ht="330.5" customHeight="1">
+      <c r="A10" s="48" t="s">
+        <v>287</v>
+      </c>
+      <c r="B10" s="48" t="s">
+        <v>305</v>
+      </c>
+      <c r="C10" s="50" t="s">
+        <v>292</v>
+      </c>
+      <c r="D10" s="50" t="s">
+        <v>293</v>
+      </c>
+      <c r="E10" s="43" t="s">
+        <v>306</v>
+      </c>
+      <c r="F10" s="43" t="s">
+        <v>307</v>
+      </c>
+      <c r="G10" s="43" t="s">
+        <v>297</v>
+      </c>
+      <c r="H10" s="48" t="s">
+        <v>51</v>
+      </c>
+      <c r="I10" s="48" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" s="46" customFormat="1" ht="330.5" customHeight="1">
+      <c r="A11" s="48" t="s">
+        <v>288</v>
+      </c>
+      <c r="B11" s="48" t="s">
+        <v>308</v>
+      </c>
+      <c r="C11" s="50" t="s">
+        <v>292</v>
+      </c>
+      <c r="D11" s="50" t="s">
+        <v>293</v>
+      </c>
+      <c r="E11" s="43" t="s">
+        <v>309</v>
+      </c>
+      <c r="F11" s="43" t="s">
+        <v>307</v>
+      </c>
+      <c r="G11" s="43" t="s">
+        <v>297</v>
+      </c>
+      <c r="H11" s="48" t="s">
+        <v>51</v>
+      </c>
+      <c r="I11" s="48" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" s="46" customFormat="1" ht="330.5" customHeight="1">
+      <c r="A12" s="48" t="s">
+        <v>289</v>
+      </c>
+      <c r="B12" s="48" t="s">
+        <v>310</v>
+      </c>
+      <c r="C12" s="50" t="s">
+        <v>292</v>
+      </c>
+      <c r="D12" s="50" t="s">
+        <v>293</v>
+      </c>
+      <c r="E12" s="43" t="s">
+        <v>311</v>
+      </c>
+      <c r="F12" s="43" t="s">
+        <v>307</v>
+      </c>
+      <c r="G12" s="43" t="s">
+        <v>297</v>
+      </c>
+      <c r="H12" s="48" t="s">
+        <v>51</v>
+      </c>
+      <c r="I12" s="48" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" s="46" customFormat="1" ht="330.5" customHeight="1">
+      <c r="A13" s="48" t="s">
+        <v>290</v>
+      </c>
+      <c r="B13" s="48" t="s">
+        <v>312</v>
+      </c>
+      <c r="C13" s="50" t="s">
+        <v>292</v>
+      </c>
+      <c r="D13" s="50" t="s">
+        <v>293</v>
+      </c>
+      <c r="E13" s="43" t="s">
+        <v>313</v>
+      </c>
+      <c r="F13" s="43" t="s">
+        <v>307</v>
+      </c>
+      <c r="G13" s="43" t="s">
+        <v>297</v>
+      </c>
+      <c r="H13" s="48" t="s">
+        <v>51</v>
+      </c>
+      <c r="I13" s="48" t="s">
+        <v>55</v>
+      </c>
+      <c r="J13" s="82"/>
+      <c r="K13" s="82"/>
+    </row>
+    <row r="14" spans="1:11" s="46" customFormat="1">
+      <c r="A14" s="75"/>
+      <c r="B14" s="75"/>
+      <c r="C14" s="77"/>
+      <c r="D14" s="78"/>
+      <c r="E14" s="79"/>
+      <c r="F14" s="80"/>
+      <c r="G14" s="80"/>
+      <c r="H14" s="75"/>
+      <c r="I14" s="75"/>
+      <c r="J14" s="82"/>
+      <c r="K14" s="82"/>
+    </row>
+    <row r="15" spans="1:11" s="46" customFormat="1">
+      <c r="A15" s="75"/>
+      <c r="B15" s="75"/>
+      <c r="C15" s="77"/>
+      <c r="D15" s="78"/>
+      <c r="E15" s="79"/>
+      <c r="F15" s="80"/>
+      <c r="G15" s="80"/>
+      <c r="H15" s="75"/>
+      <c r="I15" s="75"/>
+      <c r="J15" s="82"/>
+      <c r="K15" s="82"/>
+    </row>
+    <row r="16" spans="1:11" s="46" customFormat="1">
+      <c r="A16" s="75"/>
+      <c r="B16" s="75"/>
+      <c r="C16" s="77"/>
+      <c r="D16" s="78"/>
+      <c r="E16" s="79"/>
+      <c r="F16" s="80"/>
+      <c r="G16" s="80"/>
+      <c r="H16" s="75"/>
+      <c r="I16" s="75"/>
+      <c r="J16" s="82"/>
+      <c r="K16" s="82"/>
+    </row>
+    <row r="17" spans="1:9" s="46" customFormat="1">
+      <c r="A17" s="75"/>
+      <c r="B17" s="75"/>
+      <c r="C17" s="77"/>
+      <c r="D17" s="78"/>
+      <c r="E17" s="79"/>
+      <c r="F17" s="80"/>
+      <c r="G17" s="80"/>
+      <c r="H17" s="75"/>
+      <c r="I17" s="75"/>
+    </row>
+    <row r="18" spans="1:9" s="46" customFormat="1">
+      <c r="A18" s="75"/>
+      <c r="B18" s="75"/>
+      <c r="C18" s="77"/>
+      <c r="D18" s="78"/>
+      <c r="E18" s="79"/>
+      <c r="F18" s="80"/>
+      <c r="G18" s="80"/>
+      <c r="H18" s="75"/>
+      <c r="I18" s="75"/>
+    </row>
+    <row r="19" spans="1:9" ht="16.5" customHeight="1">
+      <c r="A19" s="75"/>
+      <c r="B19" s="81"/>
+      <c r="C19" s="77"/>
+      <c r="D19" s="77"/>
+      <c r="E19" s="79"/>
+      <c r="F19" s="79"/>
+      <c r="G19" s="79"/>
+      <c r="H19" s="75"/>
+      <c r="I19" s="75"/>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="49"/>
+      <c r="B20" s="53"/>
+      <c r="C20" s="53"/>
+      <c r="D20" s="53"/>
+      <c r="E20" s="53"/>
+      <c r="F20" s="53"/>
+      <c r="G20" s="53"/>
+      <c r="I20" s="49"/>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="49"/>
+      <c r="B21" s="53"/>
+      <c r="C21" s="53"/>
+      <c r="D21" s="53"/>
+      <c r="E21" s="53"/>
+      <c r="F21" s="53"/>
+      <c r="G21" s="53"/>
+      <c r="I21" s="49"/>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="49"/>
+      <c r="B22" s="53"/>
+      <c r="C22" s="53"/>
+      <c r="D22" s="53"/>
+      <c r="E22" s="53"/>
+      <c r="F22" s="53"/>
+      <c r="G22" s="53"/>
+      <c r="I22" s="49"/>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="49"/>
+      <c r="B23" s="53"/>
+      <c r="C23" s="53"/>
+      <c r="D23" s="53"/>
+      <c r="E23" s="53"/>
+      <c r="F23" s="53"/>
+      <c r="G23" s="53"/>
+      <c r="I23" s="49"/>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="49"/>
+      <c r="B24" s="53"/>
+      <c r="C24" s="53"/>
+      <c r="D24" s="53"/>
+      <c r="E24" s="53"/>
+      <c r="F24" s="53"/>
+      <c r="G24" s="53"/>
+      <c r="I24" s="49"/>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="49"/>
+      <c r="B25" s="53"/>
+      <c r="C25" s="53"/>
+      <c r="D25" s="53"/>
+      <c r="E25" s="53"/>
+      <c r="F25" s="53"/>
+      <c r="G25" s="53"/>
+      <c r="I25" s="49"/>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="49"/>
+      <c r="B26" s="53"/>
+      <c r="C26" s="53"/>
+      <c r="D26" s="53"/>
+      <c r="E26" s="53"/>
+      <c r="F26" s="53"/>
+      <c r="G26" s="53"/>
+      <c r="I26" s="49"/>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="49"/>
+      <c r="B27" s="53"/>
+      <c r="C27" s="53"/>
+      <c r="D27" s="53"/>
+      <c r="E27" s="53"/>
+      <c r="F27" s="53"/>
+      <c r="G27" s="53"/>
+      <c r="I27" s="49"/>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="49"/>
+      <c r="B28" s="53"/>
+      <c r="C28" s="53"/>
+      <c r="D28" s="53"/>
+      <c r="E28" s="53"/>
+      <c r="F28" s="53"/>
+      <c r="G28" s="53"/>
+      <c r="I28" s="49"/>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="47"/>
+      <c r="B29" s="46"/>
+      <c r="C29" s="46"/>
+      <c r="D29" s="46"/>
+      <c r="E29" s="46"/>
+      <c r="F29" s="46"/>
+      <c r="G29" s="46"/>
+      <c r="I29" s="47"/>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" s="47"/>
+      <c r="B30" s="46"/>
+      <c r="C30" s="46"/>
+      <c r="D30" s="46"/>
+      <c r="E30" s="46"/>
+      <c r="F30" s="46"/>
+      <c r="G30" s="46"/>
+      <c r="I30" s="47"/>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" s="47"/>
+      <c r="B31" s="46"/>
+      <c r="C31" s="46"/>
+      <c r="D31" s="46"/>
+      <c r="E31" s="46"/>
+      <c r="F31" s="46"/>
+      <c r="G31" s="46"/>
+      <c r="I31" s="47"/>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" s="47"/>
+      <c r="B32" s="46"/>
+      <c r="C32" s="46"/>
+      <c r="D32" s="46"/>
+      <c r="E32" s="46"/>
+      <c r="F32" s="46"/>
+      <c r="G32" s="46"/>
+      <c r="I32" s="47"/>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" s="47"/>
+      <c r="B33" s="46"/>
+      <c r="C33" s="46"/>
+      <c r="D33" s="46"/>
+      <c r="E33" s="46"/>
+      <c r="F33" s="46"/>
+      <c r="G33" s="46"/>
+      <c r="I33" s="47"/>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" s="47"/>
+      <c r="B34" s="46"/>
+      <c r="C34" s="46"/>
+      <c r="D34" s="46"/>
+      <c r="E34" s="46"/>
+      <c r="F34" s="46"/>
+      <c r="G34" s="46"/>
+      <c r="I34" s="47"/>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" s="47"/>
+      <c r="B35" s="46"/>
+      <c r="C35" s="46"/>
+      <c r="D35" s="46"/>
+      <c r="E35" s="46"/>
+      <c r="F35" s="46"/>
+      <c r="G35" s="46"/>
+      <c r="I35" s="47"/>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" s="47"/>
+      <c r="B36" s="46"/>
+      <c r="C36" s="46"/>
+      <c r="D36" s="46"/>
+      <c r="E36" s="46"/>
+      <c r="F36" s="46"/>
+      <c r="G36" s="46"/>
+      <c r="I36" s="47"/>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" s="47"/>
+      <c r="B37" s="46"/>
+      <c r="C37" s="46"/>
+      <c r="D37" s="46"/>
+      <c r="E37" s="46"/>
+      <c r="F37" s="46"/>
+      <c r="G37" s="46"/>
+      <c r="I37" s="47"/>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" s="47"/>
+      <c r="B38" s="46"/>
+      <c r="C38" s="46"/>
+      <c r="D38" s="46"/>
+      <c r="E38" s="46"/>
+      <c r="F38" s="46"/>
+      <c r="G38" s="46"/>
+      <c r="I38" s="47"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A1" location="'Test report'!A1" display="Back to TestReport"/>
+    <hyperlink ref="B1" location="BugList!A1" display="To Buglist"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="1" operator="containsText" id="{39F2EF52-828C-4357-9BB3-67B39B3DDF81}">
+            <xm:f>NOT(ISERROR(SEARCH(Chung!$K$20,H5)))</xm:f>
+            <xm:f>Chung!$K$20</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFF7C80"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="2" operator="containsText" id="{29FD8162-AE07-476C-A341-F405FE9F5C1A}">
+            <xm:f>NOT(ISERROR(SEARCH(Chung!$K$19,H5)))</xm:f>
+            <xm:f>Chung!$K$19</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor theme="9" tint="0.39994506668294322"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>H5:H19</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="3" operator="containsText" id="{3DFF97A9-37A6-495C-8B6A-809A49B54993}">
+            <xm:f>NOT(ISERROR(SEARCH(Chung!$L$20,I5)))</xm:f>
+            <xm:f>Chung!$L$20</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="4" operator="containsText" id="{72EED55F-270B-4255-A492-C139D3095459}">
+            <xm:f>NOT(ISERROR(SEARCH(Chung!$L$19,I5)))</xm:f>
+            <xm:f>Chung!$L$19</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor theme="7" tint="0.59996337778862885"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>I5:I19</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>Chung!$L$19:$L$20</xm:f>
+          </x14:formula1>
+          <xm:sqref>I5:I19</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>Chung!$K$19:$K$20</xm:f>
+          </x14:formula1>
+          <xm:sqref>H5:H19</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor theme="0"/>
+  </sheetPr>
   <dimension ref="A1:I47"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="16.5"/>
   <cols>
@@ -5845,7 +6859,7 @@
     <col min="2" max="2" width="24.26953125" style="13" customWidth="1"/>
     <col min="3" max="3" width="23.90625" style="13" customWidth="1"/>
     <col min="4" max="4" width="35.81640625" style="13" customWidth="1"/>
-    <col min="5" max="5" width="34.54296875" style="101" customWidth="1"/>
+    <col min="5" max="5" width="34.54296875" style="98" customWidth="1"/>
     <col min="6" max="6" width="25" style="13" customWidth="1"/>
     <col min="7" max="7" width="24.08984375" style="13" customWidth="1"/>
     <col min="8" max="8" width="8.90625" style="13"/>
@@ -5865,7 +6879,7 @@
         <f>"Pass: "&amp;COUNTIF(#REF!,"Pass")</f>
         <v>#REF!</v>
       </c>
-      <c r="E1" s="98" t="e">
+      <c r="E1" s="95" t="e">
         <f>"Untested: "&amp;COUNTIF(#REF!,"Untest")</f>
         <v>#REF!</v>
       </c>
@@ -5884,7 +6898,7 @@
         <f>"Fail: "&amp;COUNTIF(#REF!,"Fail")</f>
         <v>#REF!</v>
       </c>
-      <c r="E2" s="98" t="e">
+      <c r="E2" s="95" t="e">
         <f>"N/A: "&amp;COUNTIF(#REF!,"N/A")</f>
         <v>#REF!</v>
       </c>
@@ -5903,7 +6917,7 @@
         <f>"Percent Complete: "&amp;ROUND((COUNTIF(#REF!,"Pass")*100)/((COUNTA($A$5:$A$871)*5)-COUNTIF(#REF!,"N/A")),2)&amp;"%"</f>
         <v>#REF!</v>
       </c>
-      <c r="E3" s="99" t="str">
+      <c r="E3" s="96" t="str">
         <f>"Number of cases: "&amp;(COUNTA($A$5:$A$871))</f>
         <v>Number of cases: 13</v>
       </c>
@@ -5923,7 +6937,7 @@
       <c r="D4" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="100" t="s">
+      <c r="E4" s="97" t="s">
         <v>18</v>
       </c>
       <c r="F4" s="11" t="s">
@@ -6448,8 +7462,8 @@
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="containsText" priority="1" operator="containsText" id="{C1B0C9D6-2307-4956-8BA4-72687C7096EB}">
-            <xm:f>NOT(ISERROR(SEARCH(Chung!$K$19,H5)))</xm:f>
-            <xm:f>Chung!$K$19</xm:f>
+            <xm:f>NOT(ISERROR(SEARCH(Chung!$K$20,H5)))</xm:f>
+            <xm:f>Chung!$K$20</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -6459,8 +7473,8 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="containsText" priority="2" operator="containsText" id="{251D79C9-DEEF-4525-B19C-5E3AC8635EF0}">
-            <xm:f>NOT(ISERROR(SEARCH(Chung!$K$18,H5)))</xm:f>
-            <xm:f>Chung!$K$18</xm:f>
+            <xm:f>NOT(ISERROR(SEARCH(Chung!$K$19,H5)))</xm:f>
+            <xm:f>Chung!$K$19</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -6473,8 +7487,8 @@
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="containsText" priority="3" operator="containsText" id="{2DB35E54-CA49-4D35-9848-22E92EE439D7}">
-            <xm:f>NOT(ISERROR(SEARCH(Chung!$L$19,I5)))</xm:f>
-            <xm:f>Chung!$L$19</xm:f>
+            <xm:f>NOT(ISERROR(SEARCH(Chung!$L$20,I5)))</xm:f>
+            <xm:f>Chung!$L$20</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -6484,8 +7498,8 @@
             </x14:dxf>
           </x14:cfRule>
           <x14:cfRule type="containsText" priority="4" operator="containsText" id="{2C652850-B100-4342-BACF-3B8CAEE7C567}">
-            <xm:f>NOT(ISERROR(SEARCH(Chung!$L$18,I5)))</xm:f>
-            <xm:f>Chung!$L$18</xm:f>
+            <xm:f>NOT(ISERROR(SEARCH(Chung!$L$19,I5)))</xm:f>
+            <xm:f>Chung!$L$19</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -6502,13 +7516,13 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>Chung!$L$18:$L$19</xm:f>
+            <xm:f>Chung!$L$19:$L$20</xm:f>
           </x14:formula1>
           <xm:sqref>I5:I17</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>Chung!$K$18:$K$19</xm:f>
+            <xm:f>Chung!$K$19:$K$20</xm:f>
           </x14:formula1>
           <xm:sqref>H5:H17</xm:sqref>
         </x14:dataValidation>
